--- a/bots/jess-accounting-bot/data/live/2026 Jess Lombard Junior Dance Centre Accounting.xlsx
+++ b/bots/jess-accounting-bot/data/live/2026 Jess Lombard Junior Dance Centre Accounting.xlsx
@@ -920,7 +920,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1366"/>
+  <dimension ref="A1:I1367"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="2.88" customWidth="1" style="183" min="1" max="1"/>
@@ -33018,7 +33018,32 @@
         </is>
       </c>
     </row>
-    <row r="1367" ht="15.75" customHeight="1" s="183"/>
+    <row r="1367" ht="15.75" customHeight="1" s="183">
+      <c r="B1367" s="53" t="n">
+        <v>12</v>
+      </c>
+      <c r="C1367" s="184" t="n">
+        <v>45199</v>
+      </c>
+      <c r="D1367" s="53" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E1367" s="53" t="inlineStr">
+        <is>
+          <t>Entertainment</t>
+        </is>
+      </c>
+      <c r="F1367" s="53" t="n">
+        <v>975</v>
+      </c>
+      <c r="G1367" s="53" t="inlineStr">
+        <is>
+          <t>Customer copy approved</t>
+        </is>
+      </c>
+    </row>
     <row r="1368" ht="15.75" customHeight="1" s="183"/>
     <row r="1369" ht="15.75" customHeight="1" s="183"/>
     <row r="1370" ht="15.75" customHeight="1" s="183"/>
@@ -33416,7 +33441,7 @@
         </is>
       </c>
       <c r="C11" s="146">
-        <f>SUMIFS('Transactions Raw'!$F$3:$F1366,'Transactions Raw'!$E$3:$E1366,'FY26 Trail Balance'!$B11,'Transactions Raw'!$C$3:$C1366,"&gt;="&amp;$I$2,'Transactions Raw'!$C$3:$C1366,"&lt;="&amp;$J$2)</f>
+        <f>SUMIFS('Transactions Raw'!$F$3:$F1367,'Transactions Raw'!$E$3:$E1367,'FY26 Trail Balance'!$B11,'Transactions Raw'!$C$3:$C1367,"&gt;="&amp;$I$2,'Transactions Raw'!$C$3:$C1367,"&lt;="&amp;$J$2)</f>
         <v/>
       </c>
       <c r="D11" s="147" t="inlineStr">
@@ -33449,7 +33474,7 @@
         </is>
       </c>
       <c r="C13" s="146">
-        <f>SUMIFS('Transactions Raw'!$F$3:$F1366,'Transactions Raw'!$E$3:$E1366,'FY26 Trail Balance'!$B13,'Transactions Raw'!$C$3:$C1366,"&gt;="&amp;$I$2,'Transactions Raw'!$C$3:$C1366,"&lt;="&amp;$J$2)</f>
+        <f>SUMIFS('Transactions Raw'!$F$3:$F1367,'Transactions Raw'!$E$3:$E1367,'FY26 Trail Balance'!$B13,'Transactions Raw'!$C$3:$C1367,"&gt;="&amp;$I$2,'Transactions Raw'!$C$3:$C1367,"&lt;="&amp;$J$2)</f>
         <v/>
       </c>
       <c r="D13" s="147" t="inlineStr">
@@ -33466,7 +33491,7 @@
         </is>
       </c>
       <c r="C14" s="146">
-        <f>SUMIFS('Transactions Raw'!$F$3:$F1366,'Transactions Raw'!$E$3:$E1366,'FY26 Trail Balance'!$B14,'Transactions Raw'!$C$3:$C1366,"&gt;="&amp;$I$2,'Transactions Raw'!$C$3:$C1366,"&lt;="&amp;$J$2)</f>
+        <f>SUMIFS('Transactions Raw'!$F$3:$F1367,'Transactions Raw'!$E$3:$E1367,'FY26 Trail Balance'!$B14,'Transactions Raw'!$C$3:$C1367,"&gt;="&amp;$I$2,'Transactions Raw'!$C$3:$C1367,"&lt;="&amp;$J$2)</f>
         <v/>
       </c>
       <c r="D14" s="147" t="inlineStr">
@@ -33484,7 +33509,7 @@
         </is>
       </c>
       <c r="C15" s="146">
-        <f>SUMIFS('Transactions Raw'!$F$3:$F1366,'Transactions Raw'!$E$3:$E1366,'FY26 Trail Balance'!$B15,'Transactions Raw'!$C$3:$C1366,"&gt;="&amp;$I$2,'Transactions Raw'!$C$3:$C1366,"&lt;="&amp;$J$2)</f>
+        <f>SUMIFS('Transactions Raw'!$F$3:$F1367,'Transactions Raw'!$E$3:$E1367,'FY26 Trail Balance'!$B15,'Transactions Raw'!$C$3:$C1367,"&gt;="&amp;$I$2,'Transactions Raw'!$C$3:$C1367,"&lt;="&amp;$J$2)</f>
         <v/>
       </c>
       <c r="D15" s="147" t="inlineStr">
@@ -33502,7 +33527,7 @@
         </is>
       </c>
       <c r="C16" s="146">
-        <f>SUMIFS('Transactions Raw'!$F$3:$F1366,'Transactions Raw'!$E$3:$E1366,'FY26 Trail Balance'!$B16,'Transactions Raw'!$C$3:$C1366,"&gt;="&amp;$I$2,'Transactions Raw'!$C$3:$C1366,"&lt;="&amp;$J$2)</f>
+        <f>SUMIFS('Transactions Raw'!$F$3:$F1367,'Transactions Raw'!$E$3:$E1367,'FY26 Trail Balance'!$B16,'Transactions Raw'!$C$3:$C1367,"&gt;="&amp;$I$2,'Transactions Raw'!$C$3:$C1367,"&lt;="&amp;$J$2)</f>
         <v/>
       </c>
       <c r="D16" s="147" t="inlineStr">
@@ -33520,7 +33545,7 @@
         </is>
       </c>
       <c r="C17" s="146">
-        <f>SUMIFS('Transactions Raw'!$F$3:$F1366,'Transactions Raw'!$E$3:$E1366,'FY26 Trail Balance'!$B17,'Transactions Raw'!$C$3:$C1366,"&gt;="&amp;$I$2,'Transactions Raw'!$C$3:$C1366,"&lt;="&amp;$J$2)</f>
+        <f>SUMIFS('Transactions Raw'!$F$3:$F1367,'Transactions Raw'!$E$3:$E1367,'FY26 Trail Balance'!$B17,'Transactions Raw'!$C$3:$C1367,"&gt;="&amp;$I$2,'Transactions Raw'!$C$3:$C1367,"&lt;="&amp;$J$2)</f>
         <v/>
       </c>
       <c r="D17" s="147" t="inlineStr">
@@ -33538,7 +33563,7 @@
         </is>
       </c>
       <c r="C18" s="146">
-        <f>SUMIFS('Transactions Raw'!$F$3:$F1366,'Transactions Raw'!$E$3:$E1366,'FY26 Trail Balance'!$B18,'Transactions Raw'!$C$3:$C1366,"&gt;="&amp;$I$2,'Transactions Raw'!$C$3:$C1366,"&lt;="&amp;$J$2)</f>
+        <f>SUMIFS('Transactions Raw'!$F$3:$F1367,'Transactions Raw'!$E$3:$E1367,'FY26 Trail Balance'!$B18,'Transactions Raw'!$C$3:$C1367,"&gt;="&amp;$I$2,'Transactions Raw'!$C$3:$C1367,"&lt;="&amp;$J$2)</f>
         <v/>
       </c>
       <c r="D18" s="147" t="inlineStr">
@@ -33555,7 +33580,7 @@
         </is>
       </c>
       <c r="C19" s="146">
-        <f>SUMIFS('Transactions Raw'!$F$3:$F1366,'Transactions Raw'!$E$3:$E1366,'FY26 Trail Balance'!$B19,'Transactions Raw'!$C$3:$C1366,"&gt;="&amp;$I$2,'Transactions Raw'!$C$3:$C1366,"&lt;="&amp;$J$2)</f>
+        <f>SUMIFS('Transactions Raw'!$F$3:$F1367,'Transactions Raw'!$E$3:$E1367,'FY26 Trail Balance'!$B19,'Transactions Raw'!$C$3:$C1367,"&gt;="&amp;$I$2,'Transactions Raw'!$C$3:$C1367,"&lt;="&amp;$J$2)</f>
         <v/>
       </c>
       <c r="D19" s="147" t="inlineStr">
@@ -33572,7 +33597,7 @@
         </is>
       </c>
       <c r="C20" s="146">
-        <f>SUMIFS('Transactions Raw'!$F$3:$F1366,'Transactions Raw'!$E$3:$E1366,'FY26 Trail Balance'!$B20,'Transactions Raw'!$C$3:$C1366,"&gt;="&amp;$I$2,'Transactions Raw'!$C$3:$C1366,"&lt;="&amp;$J$2)</f>
+        <f>SUMIFS('Transactions Raw'!$F$3:$F1367,'Transactions Raw'!$E$3:$E1367,'FY26 Trail Balance'!$B20,'Transactions Raw'!$C$3:$C1367,"&gt;="&amp;$I$2,'Transactions Raw'!$C$3:$C1367,"&lt;="&amp;$J$2)</f>
         <v/>
       </c>
       <c r="D20" s="147" t="inlineStr">
@@ -33589,7 +33614,7 @@
         </is>
       </c>
       <c r="C21" s="146">
-        <f>SUMIFS('Transactions Raw'!$F$3:$F1366,'Transactions Raw'!$E$3:$E1366,'FY26 Trail Balance'!$B21,'Transactions Raw'!$C$3:$C1366,"&gt;="&amp;$I$2,'Transactions Raw'!$C$3:$C1366,"&lt;="&amp;$J$2)</f>
+        <f>SUMIFS('Transactions Raw'!$F$3:$F1367,'Transactions Raw'!$E$3:$E1367,'FY26 Trail Balance'!$B21,'Transactions Raw'!$C$3:$C1367,"&gt;="&amp;$I$2,'Transactions Raw'!$C$3:$C1367,"&lt;="&amp;$J$2)</f>
         <v/>
       </c>
       <c r="D21" s="147" t="inlineStr">
@@ -33606,7 +33631,7 @@
         </is>
       </c>
       <c r="C22" s="146">
-        <f>SUMIFS('Transactions Raw'!$F$3:$F1366,'Transactions Raw'!$E$3:$E1366,'FY26 Trail Balance'!$B22,'Transactions Raw'!$C$3:$C1366,"&gt;="&amp;$I$2,'Transactions Raw'!$C$3:$C1366,"&lt;="&amp;$J$2)</f>
+        <f>SUMIFS('Transactions Raw'!$F$3:$F1367,'Transactions Raw'!$E$3:$E1367,'FY26 Trail Balance'!$B22,'Transactions Raw'!$C$3:$C1367,"&gt;="&amp;$I$2,'Transactions Raw'!$C$3:$C1367,"&lt;="&amp;$J$2)</f>
         <v/>
       </c>
       <c r="D22" s="147" t="inlineStr">
@@ -33623,7 +33648,7 @@
         </is>
       </c>
       <c r="C23" s="146">
-        <f>SUMIFS('Transactions Raw'!$F$3:$F1366,'Transactions Raw'!$E$3:$E1366,'FY26 Trail Balance'!$B23,'Transactions Raw'!$C$3:$C1366,"&gt;="&amp;$I$2,'Transactions Raw'!$C$3:$C1366,"&lt;="&amp;$J$2)</f>
+        <f>SUMIFS('Transactions Raw'!$F$3:$F1367,'Transactions Raw'!$E$3:$E1367,'FY26 Trail Balance'!$B23,'Transactions Raw'!$C$3:$C1367,"&gt;="&amp;$I$2,'Transactions Raw'!$C$3:$C1367,"&lt;="&amp;$J$2)</f>
         <v/>
       </c>
       <c r="D23" s="147" t="inlineStr">
@@ -33640,7 +33665,7 @@
         </is>
       </c>
       <c r="C24" s="146">
-        <f>SUMIFS('Transactions Raw'!$F$3:$F1366,'Transactions Raw'!$E$3:$E1366,'FY26 Trail Balance'!$B24,'Transactions Raw'!$C$3:$C1366,"&gt;="&amp;$I$2,'Transactions Raw'!$C$3:$C1366,"&lt;="&amp;$J$2)</f>
+        <f>SUMIFS('Transactions Raw'!$F$3:$F1367,'Transactions Raw'!$E$3:$E1367,'FY26 Trail Balance'!$B24,'Transactions Raw'!$C$3:$C1367,"&gt;="&amp;$I$2,'Transactions Raw'!$C$3:$C1367,"&lt;="&amp;$J$2)</f>
         <v/>
       </c>
       <c r="D24" s="147" t="inlineStr">
@@ -33657,7 +33682,7 @@
         </is>
       </c>
       <c r="C25" s="146">
-        <f>SUMIFS('Transactions Raw'!$F$3:$F1366,'Transactions Raw'!$E$3:$E1366,'FY26 Trail Balance'!$B25,'Transactions Raw'!$C$3:$C1366,"&gt;="&amp;$I$2,'Transactions Raw'!$C$3:$C1366,"&lt;="&amp;$J$2)</f>
+        <f>SUMIFS('Transactions Raw'!$F$3:$F1367,'Transactions Raw'!$E$3:$E1367,'FY26 Trail Balance'!$B25,'Transactions Raw'!$C$3:$C1367,"&gt;="&amp;$I$2,'Transactions Raw'!$C$3:$C1367,"&lt;="&amp;$J$2)</f>
         <v/>
       </c>
       <c r="D25" s="147" t="inlineStr">
@@ -33674,7 +33699,7 @@
         </is>
       </c>
       <c r="C26" s="146">
-        <f>SUMIFS('Transactions Raw'!$F$3:$F1366,'Transactions Raw'!$E$3:$E1366,'FY26 Trail Balance'!$B26,'Transactions Raw'!$C$3:$C1366,"&gt;="&amp;$I$2,'Transactions Raw'!$C$3:$C1366,"&lt;="&amp;$J$2)</f>
+        <f>SUMIFS('Transactions Raw'!$F$3:$F1367,'Transactions Raw'!$E$3:$E1367,'FY26 Trail Balance'!$B26,'Transactions Raw'!$C$3:$C1367,"&gt;="&amp;$I$2,'Transactions Raw'!$C$3:$C1367,"&lt;="&amp;$J$2)</f>
         <v/>
       </c>
       <c r="D26" s="147" t="inlineStr">
@@ -33691,7 +33716,7 @@
         </is>
       </c>
       <c r="C27" s="146">
-        <f>SUMIFS('Transactions Raw'!$F$3:$F1366,'Transactions Raw'!$E$3:$E1366,'FY26 Trail Balance'!$B27,'Transactions Raw'!$C$3:$C1366,"&gt;="&amp;$I$2,'Transactions Raw'!$C$3:$C1366,"&lt;="&amp;$J$2)</f>
+        <f>SUMIFS('Transactions Raw'!$F$3:$F1367,'Transactions Raw'!$E$3:$E1367,'FY26 Trail Balance'!$B27,'Transactions Raw'!$C$3:$C1367,"&gt;="&amp;$I$2,'Transactions Raw'!$C$3:$C1367,"&lt;="&amp;$J$2)</f>
         <v/>
       </c>
       <c r="D27" s="147" t="inlineStr">
@@ -33708,7 +33733,7 @@
         </is>
       </c>
       <c r="C28" s="146">
-        <f>SUMIFS('Transactions Raw'!$F$3:$F1366,'Transactions Raw'!$E$3:$E1366,'FY26 Trail Balance'!$B28,'Transactions Raw'!$C$3:$C1366,"&gt;="&amp;$I$2,'Transactions Raw'!$C$3:$C1366,"&lt;="&amp;$J$2)</f>
+        <f>SUMIFS('Transactions Raw'!$F$3:$F1367,'Transactions Raw'!$E$3:$E1367,'FY26 Trail Balance'!$B28,'Transactions Raw'!$C$3:$C1367,"&gt;="&amp;$I$2,'Transactions Raw'!$C$3:$C1367,"&lt;="&amp;$J$2)</f>
         <v/>
       </c>
       <c r="D28" s="147" t="inlineStr">
@@ -33725,7 +33750,7 @@
         </is>
       </c>
       <c r="C29" s="146">
-        <f>SUMIFS('Transactions Raw'!$F$3:$F1366,'Transactions Raw'!$E$3:$E1366,'FY26 Trail Balance'!$B29,'Transactions Raw'!$C$3:$C1366,"&gt;="&amp;$I$2,'Transactions Raw'!$C$3:$C1366,"&lt;="&amp;$J$2)</f>
+        <f>SUMIFS('Transactions Raw'!$F$3:$F1367,'Transactions Raw'!$E$3:$E1367,'FY26 Trail Balance'!$B29,'Transactions Raw'!$C$3:$C1367,"&gt;="&amp;$I$2,'Transactions Raw'!$C$3:$C1367,"&lt;="&amp;$J$2)</f>
         <v/>
       </c>
       <c r="D29" s="147" t="inlineStr">
@@ -33743,7 +33768,7 @@
         </is>
       </c>
       <c r="C30" s="146">
-        <f>SUMIFS('Transactions Raw'!$F$3:$F1366,'Transactions Raw'!$E$3:$E1366,'FY26 Trail Balance'!$B30,'Transactions Raw'!$C$3:$C1366,"&gt;="&amp;$I$2,'Transactions Raw'!$C$3:$C1366,"&lt;="&amp;$J$2)</f>
+        <f>SUMIFS('Transactions Raw'!$F$3:$F1367,'Transactions Raw'!$E$3:$E1367,'FY26 Trail Balance'!$B30,'Transactions Raw'!$C$3:$C1367,"&gt;="&amp;$I$2,'Transactions Raw'!$C$3:$C1367,"&lt;="&amp;$J$2)</f>
         <v/>
       </c>
       <c r="D30" s="147" t="inlineStr">
@@ -33761,7 +33786,7 @@
         </is>
       </c>
       <c r="C31" s="146">
-        <f>SUMIFS('Transactions Raw'!$F$3:$F1366,'Transactions Raw'!$E$3:$E1366,'FY26 Trail Balance'!$B31,'Transactions Raw'!$C$3:$C1366,"&gt;="&amp;$I$2,'Transactions Raw'!$C$3:$C1366,"&lt;="&amp;$J$2)</f>
+        <f>SUMIFS('Transactions Raw'!$F$3:$F1367,'Transactions Raw'!$E$3:$E1367,'FY26 Trail Balance'!$B31,'Transactions Raw'!$C$3:$C1367,"&gt;="&amp;$I$2,'Transactions Raw'!$C$3:$C1367,"&lt;="&amp;$J$2)</f>
         <v/>
       </c>
       <c r="D31" s="147" t="inlineStr">
@@ -33779,7 +33804,7 @@
         </is>
       </c>
       <c r="C32" s="146">
-        <f>SUMIFS('Transactions Raw'!$F$3:$F1366,'Transactions Raw'!$E$3:$E1366,'FY26 Trail Balance'!$B32,'Transactions Raw'!$C$3:$C1366,"&gt;="&amp;$I$2,'Transactions Raw'!$C$3:$C1366,"&lt;="&amp;$J$2)</f>
+        <f>SUMIFS('Transactions Raw'!$F$3:$F1367,'Transactions Raw'!$E$3:$E1367,'FY26 Trail Balance'!$B32,'Transactions Raw'!$C$3:$C1367,"&gt;="&amp;$I$2,'Transactions Raw'!$C$3:$C1367,"&lt;="&amp;$J$2)</f>
         <v/>
       </c>
       <c r="D32" s="147" t="inlineStr">
@@ -33797,7 +33822,7 @@
         </is>
       </c>
       <c r="C33" s="146">
-        <f>SUMIFS('Transactions Raw'!$F$3:$F1366,'Transactions Raw'!$E$3:$E1366,'FY26 Trail Balance'!$B33,'Transactions Raw'!$C$3:$C1366,"&gt;="&amp;$I$2,'Transactions Raw'!$C$3:$C1366,"&lt;="&amp;$J$2)</f>
+        <f>SUMIFS('Transactions Raw'!$F$3:$F1367,'Transactions Raw'!$E$3:$E1367,'FY26 Trail Balance'!$B33,'Transactions Raw'!$C$3:$C1367,"&gt;="&amp;$I$2,'Transactions Raw'!$C$3:$C1367,"&lt;="&amp;$J$2)</f>
         <v/>
       </c>
       <c r="D33" s="147" t="inlineStr">
@@ -33815,7 +33840,7 @@
         </is>
       </c>
       <c r="C34" s="146">
-        <f>SUMIFS('Transactions Raw'!$F$3:$F1366,'Transactions Raw'!$E$3:$E1366,'FY26 Trail Balance'!$B34,'Transactions Raw'!$C$3:$C1366,"&gt;="&amp;$I$2,'Transactions Raw'!$C$3:$C1366,"&lt;="&amp;$J$2)</f>
+        <f>SUMIFS('Transactions Raw'!$F$3:$F1367,'Transactions Raw'!$E$3:$E1367,'FY26 Trail Balance'!$B34,'Transactions Raw'!$C$3:$C1367,"&gt;="&amp;$I$2,'Transactions Raw'!$C$3:$C1367,"&lt;="&amp;$J$2)</f>
         <v/>
       </c>
       <c r="D34" s="147" t="inlineStr">
@@ -33833,7 +33858,7 @@
         </is>
       </c>
       <c r="C35" s="146">
-        <f>SUMIFS('Transactions Raw'!$F$3:$F1366,'Transactions Raw'!$E$3:$E1366,'FY26 Trail Balance'!$B35,'Transactions Raw'!$C$3:$C1366,"&gt;="&amp;$I$2,'Transactions Raw'!$C$3:$C1366,"&lt;="&amp;$J$2)</f>
+        <f>SUMIFS('Transactions Raw'!$F$3:$F1367,'Transactions Raw'!$E$3:$E1367,'FY26 Trail Balance'!$B35,'Transactions Raw'!$C$3:$C1367,"&gt;="&amp;$I$2,'Transactions Raw'!$C$3:$C1367,"&lt;="&amp;$J$2)</f>
         <v/>
       </c>
       <c r="D35" s="147" t="inlineStr">
@@ -33851,7 +33876,7 @@
         </is>
       </c>
       <c r="C36" s="146">
-        <f>SUMIFS('Transactions Raw'!$F$3:$F1366,'Transactions Raw'!$E$3:$E1366,'FY26 Trail Balance'!$B36,'Transactions Raw'!$C$3:$C1366,"&gt;="&amp;$I$2,'Transactions Raw'!$C$3:$C1366,"&lt;="&amp;$J$2)</f>
+        <f>SUMIFS('Transactions Raw'!$F$3:$F1367,'Transactions Raw'!$E$3:$E1367,'FY26 Trail Balance'!$B36,'Transactions Raw'!$C$3:$C1367,"&gt;="&amp;$I$2,'Transactions Raw'!$C$3:$C1367,"&lt;="&amp;$J$2)</f>
         <v/>
       </c>
       <c r="D36" s="147" t="inlineStr">
@@ -33869,7 +33894,7 @@
         </is>
       </c>
       <c r="C37" s="146">
-        <f>SUMIFS('Transactions Raw'!$F$3:$F1366,'Transactions Raw'!$E$3:$E1366,'FY26 Trail Balance'!$B37,'Transactions Raw'!$C$3:$C1366,"&gt;="&amp;$I$2,'Transactions Raw'!$C$3:$C1366,"&lt;="&amp;$J$2)</f>
+        <f>SUMIFS('Transactions Raw'!$F$3:$F1367,'Transactions Raw'!$E$3:$E1367,'FY26 Trail Balance'!$B37,'Transactions Raw'!$C$3:$C1367,"&gt;="&amp;$I$2,'Transactions Raw'!$C$3:$C1367,"&lt;="&amp;$J$2)</f>
         <v/>
       </c>
       <c r="D37" s="155" t="inlineStr">
@@ -33886,7 +33911,7 @@
         </is>
       </c>
       <c r="C38" s="146">
-        <f>SUMIFS('Transactions Raw'!$F$3:$F1366,'Transactions Raw'!$E$3:$E1366,'FY26 Trail Balance'!$B38,'Transactions Raw'!$C$3:$C1366,"&gt;="&amp;$I$2,'Transactions Raw'!$C$3:$C1366,"&lt;="&amp;$J$2)</f>
+        <f>SUMIFS('Transactions Raw'!$F$3:$F1367,'Transactions Raw'!$E$3:$E1367,'FY26 Trail Balance'!$B38,'Transactions Raw'!$C$3:$C1367,"&gt;="&amp;$I$2,'Transactions Raw'!$C$3:$C1367,"&lt;="&amp;$J$2)</f>
         <v/>
       </c>
       <c r="D38" s="155" t="inlineStr">
@@ -33903,7 +33928,7 @@
         </is>
       </c>
       <c r="C39" s="146">
-        <f>SUMIFS('Transactions Raw'!$F$3:$F1366,'Transactions Raw'!$E$3:$E1366,'FY26 Trail Balance'!$B39,'Transactions Raw'!$C$3:$C1366,"&gt;="&amp;$I$2,'Transactions Raw'!$C$3:$C1366,"&lt;="&amp;$J$2)</f>
+        <f>SUMIFS('Transactions Raw'!$F$3:$F1367,'Transactions Raw'!$E$3:$E1367,'FY26 Trail Balance'!$B39,'Transactions Raw'!$C$3:$C1367,"&gt;="&amp;$I$2,'Transactions Raw'!$C$3:$C1367,"&lt;="&amp;$J$2)</f>
         <v/>
       </c>
       <c r="D39" s="155" t="inlineStr">
@@ -33920,7 +33945,7 @@
         </is>
       </c>
       <c r="C40" s="146">
-        <f>SUMIFS('Transactions Raw'!$F$3:$F1366,'Transactions Raw'!$E$3:$E1366,'FY26 Trail Balance'!$B40,'Transactions Raw'!$C$3:$C1366,"&gt;="&amp;$I$2,'Transactions Raw'!$C$3:$C1366,"&lt;="&amp;$J$2)</f>
+        <f>SUMIFS('Transactions Raw'!$F$3:$F1367,'Transactions Raw'!$E$3:$E1367,'FY26 Trail Balance'!$B40,'Transactions Raw'!$C$3:$C1367,"&gt;="&amp;$I$2,'Transactions Raw'!$C$3:$C1367,"&lt;="&amp;$J$2)</f>
         <v/>
       </c>
       <c r="D40" s="155" t="inlineStr">
@@ -33937,7 +33962,7 @@
         </is>
       </c>
       <c r="C41" s="146">
-        <f>SUMIFS('Transactions Raw'!$F$3:$F1366,'Transactions Raw'!$E$3:$E1366,'FY26 Trail Balance'!$B41,'Transactions Raw'!$C$3:$C1366,"&gt;="&amp;$I$2,'Transactions Raw'!$C$3:$C1366,"&lt;="&amp;$J$2)</f>
+        <f>SUMIFS('Transactions Raw'!$F$3:$F1367,'Transactions Raw'!$E$3:$E1367,'FY26 Trail Balance'!$B41,'Transactions Raw'!$C$3:$C1367,"&gt;="&amp;$I$2,'Transactions Raw'!$C$3:$C1367,"&lt;="&amp;$J$2)</f>
         <v/>
       </c>
       <c r="D41" s="155" t="inlineStr">
@@ -33954,7 +33979,7 @@
         </is>
       </c>
       <c r="C42" s="146">
-        <f>SUMIFS('Transactions Raw'!$F$3:$F1366,'Transactions Raw'!$E$3:$E1366,'FY26 Trail Balance'!$B42,'Transactions Raw'!$C$3:$C1366,"&gt;="&amp;$I$2,'Transactions Raw'!$C$3:$C1366,"&lt;="&amp;$J$2)</f>
+        <f>SUMIFS('Transactions Raw'!$F$3:$F1367,'Transactions Raw'!$E$3:$E1367,'FY26 Trail Balance'!$B42,'Transactions Raw'!$C$3:$C1367,"&gt;="&amp;$I$2,'Transactions Raw'!$C$3:$C1367,"&lt;="&amp;$J$2)</f>
         <v/>
       </c>
       <c r="D42" s="155" t="inlineStr">
@@ -33971,7 +33996,7 @@
         </is>
       </c>
       <c r="C43" s="146">
-        <f>SUMIFS('Transactions Raw'!$F$3:$F1366,'Transactions Raw'!$E$3:$E1366,'FY26 Trail Balance'!$B43,'Transactions Raw'!$C$3:$C1366,"&gt;="&amp;$I$2,'Transactions Raw'!$C$3:$C1366,"&lt;="&amp;$J$2)</f>
+        <f>SUMIFS('Transactions Raw'!$F$3:$F1367,'Transactions Raw'!$E$3:$E1367,'FY26 Trail Balance'!$B43,'Transactions Raw'!$C$3:$C1367,"&gt;="&amp;$I$2,'Transactions Raw'!$C$3:$C1367,"&lt;="&amp;$J$2)</f>
         <v/>
       </c>
       <c r="D43" s="155" t="inlineStr">
@@ -33988,7 +34013,7 @@
         </is>
       </c>
       <c r="C44" s="146">
-        <f>SUMIFS('Transactions Raw'!$F$3:$F1366,'Transactions Raw'!$E$3:$E1366,'FY26 Trail Balance'!$B44,'Transactions Raw'!$C$3:$C1366,"&gt;="&amp;$I$2,'Transactions Raw'!$C$3:$C1366,"&lt;="&amp;$J$2)</f>
+        <f>SUMIFS('Transactions Raw'!$F$3:$F1367,'Transactions Raw'!$E$3:$E1367,'FY26 Trail Balance'!$B44,'Transactions Raw'!$C$3:$C1367,"&gt;="&amp;$I$2,'Transactions Raw'!$C$3:$C1367,"&lt;="&amp;$J$2)</f>
         <v/>
       </c>
       <c r="D44" s="155" t="inlineStr">
@@ -34005,7 +34030,7 @@
         </is>
       </c>
       <c r="C45" s="146">
-        <f>SUMIFS('Transactions Raw'!$F$3:$F1366,'Transactions Raw'!$E$3:$E1366,'FY26 Trail Balance'!$B45,'Transactions Raw'!$C$3:$C1366,"&gt;="&amp;$I$2,'Transactions Raw'!$C$3:$C1366,"&lt;="&amp;$J$2)</f>
+        <f>SUMIFS('Transactions Raw'!$F$3:$F1367,'Transactions Raw'!$E$3:$E1367,'FY26 Trail Balance'!$B45,'Transactions Raw'!$C$3:$C1367,"&gt;="&amp;$I$2,'Transactions Raw'!$C$3:$C1367,"&lt;="&amp;$J$2)</f>
         <v/>
       </c>
       <c r="D45" s="155" t="inlineStr">
@@ -34022,7 +34047,7 @@
         </is>
       </c>
       <c r="C46" s="146">
-        <f>SUMIFS('Transactions Raw'!$F$3:$F1366,'Transactions Raw'!$E$3:$E1366,'FY26 Trail Balance'!$B46,'Transactions Raw'!$C$3:$C1366,"&gt;="&amp;$I$2,'Transactions Raw'!$C$3:$C1366,"&lt;="&amp;$J$2)</f>
+        <f>SUMIFS('Transactions Raw'!$F$3:$F1367,'Transactions Raw'!$E$3:$E1367,'FY26 Trail Balance'!$B46,'Transactions Raw'!$C$3:$C1367,"&gt;="&amp;$I$2,'Transactions Raw'!$C$3:$C1367,"&lt;="&amp;$J$2)</f>
         <v/>
       </c>
       <c r="D46" s="155" t="inlineStr">
@@ -34039,7 +34064,7 @@
         </is>
       </c>
       <c r="C47" s="146">
-        <f>SUMIFS('Transactions Raw'!$F$3:$F1366,'Transactions Raw'!$E$3:$E1366,'FY26 Trail Balance'!$B47,'Transactions Raw'!$C$3:$C1366,"&gt;="&amp;$I$2,'Transactions Raw'!$C$3:$C1366,"&lt;="&amp;$J$2)</f>
+        <f>SUMIFS('Transactions Raw'!$F$3:$F1367,'Transactions Raw'!$E$3:$E1367,'FY26 Trail Balance'!$B47,'Transactions Raw'!$C$3:$C1367,"&gt;="&amp;$I$2,'Transactions Raw'!$C$3:$C1367,"&lt;="&amp;$J$2)</f>
         <v/>
       </c>
       <c r="D47" s="155" t="inlineStr">
@@ -34056,7 +34081,7 @@
         </is>
       </c>
       <c r="C48" s="146">
-        <f>SUMIFS('Transactions Raw'!$F$3:$F1366,'Transactions Raw'!$E$3:$E1366,'FY26 Trail Balance'!$B48,'Transactions Raw'!$C$3:$C1366,"&gt;="&amp;$I$2,'Transactions Raw'!$C$3:$C1366,"&lt;="&amp;$J$2)</f>
+        <f>SUMIFS('Transactions Raw'!$F$3:$F1367,'Transactions Raw'!$E$3:$E1367,'FY26 Trail Balance'!$B48,'Transactions Raw'!$C$3:$C1367,"&gt;="&amp;$I$2,'Transactions Raw'!$C$3:$C1367,"&lt;="&amp;$J$2)</f>
         <v/>
       </c>
       <c r="D48" s="155" t="inlineStr">
@@ -34073,7 +34098,7 @@
         </is>
       </c>
       <c r="C49" s="146">
-        <f>SUMIFS('Transactions Raw'!$F$3:$F1366,'Transactions Raw'!$E$3:$E1366,'FY26 Trail Balance'!$B49,'Transactions Raw'!$C$3:$C1366,"&gt;="&amp;$I$2,'Transactions Raw'!$C$3:$C1366,"&lt;="&amp;$J$2)</f>
+        <f>SUMIFS('Transactions Raw'!$F$3:$F1367,'Transactions Raw'!$E$3:$E1367,'FY26 Trail Balance'!$B49,'Transactions Raw'!$C$3:$C1367,"&gt;="&amp;$I$2,'Transactions Raw'!$C$3:$C1367,"&lt;="&amp;$J$2)</f>
         <v/>
       </c>
       <c r="D49" s="155" t="inlineStr">
@@ -34090,7 +34115,7 @@
         </is>
       </c>
       <c r="C50" s="146">
-        <f>SUMIFS('Transactions Raw'!$F$3:$F1366,'Transactions Raw'!$E$3:$E1366,'FY26 Trail Balance'!$B50,'Transactions Raw'!$C$3:$C1366,"&gt;="&amp;$I$2,'Transactions Raw'!$C$3:$C1366,"&lt;="&amp;$J$2)</f>
+        <f>SUMIFS('Transactions Raw'!$F$3:$F1367,'Transactions Raw'!$E$3:$E1367,'FY26 Trail Balance'!$B50,'Transactions Raw'!$C$3:$C1367,"&gt;="&amp;$I$2,'Transactions Raw'!$C$3:$C1367,"&lt;="&amp;$J$2)</f>
         <v/>
       </c>
       <c r="D50" s="155" t="inlineStr">
@@ -34107,7 +34132,7 @@
         </is>
       </c>
       <c r="C51" s="146">
-        <f>SUMIFS('Transactions Raw'!$F$3:$F1366,'Transactions Raw'!$E$3:$E1366,'FY26 Trail Balance'!$B51,'Transactions Raw'!$C$3:$C1366,"&gt;="&amp;$I$2,'Transactions Raw'!$C$3:$C1366,"&lt;="&amp;$J$2)</f>
+        <f>SUMIFS('Transactions Raw'!$F$3:$F1367,'Transactions Raw'!$E$3:$E1367,'FY26 Trail Balance'!$B51,'Transactions Raw'!$C$3:$C1367,"&gt;="&amp;$I$2,'Transactions Raw'!$C$3:$C1367,"&lt;="&amp;$J$2)</f>
         <v/>
       </c>
       <c r="D51" s="155" t="inlineStr">
@@ -34124,7 +34149,7 @@
         </is>
       </c>
       <c r="C52" s="146">
-        <f>SUMIFS('Transactions Raw'!$F$3:$F1366,'Transactions Raw'!$E$3:$E1366,'FY26 Trail Balance'!$B52,'Transactions Raw'!$C$3:$C1366,"&gt;="&amp;$I$2,'Transactions Raw'!$C$3:$C1366,"&lt;="&amp;$J$2)</f>
+        <f>SUMIFS('Transactions Raw'!$F$3:$F1367,'Transactions Raw'!$E$3:$E1367,'FY26 Trail Balance'!$B52,'Transactions Raw'!$C$3:$C1367,"&gt;="&amp;$I$2,'Transactions Raw'!$C$3:$C1367,"&lt;="&amp;$J$2)</f>
         <v/>
       </c>
       <c r="D52" s="155" t="inlineStr">
@@ -34141,7 +34166,7 @@
         </is>
       </c>
       <c r="C53" s="146">
-        <f>SUMIFS('Transactions Raw'!$F$3:$F1366,'Transactions Raw'!$E$3:$E1366,'FY26 Trail Balance'!$B53,'Transactions Raw'!$C$3:$C1366,"&gt;="&amp;$I$2,'Transactions Raw'!$C$3:$C1366,"&lt;="&amp;$J$2)</f>
+        <f>SUMIFS('Transactions Raw'!$F$3:$F1367,'Transactions Raw'!$E$3:$E1367,'FY26 Trail Balance'!$B53,'Transactions Raw'!$C$3:$C1367,"&gt;="&amp;$I$2,'Transactions Raw'!$C$3:$C1367,"&lt;="&amp;$J$2)</f>
         <v/>
       </c>
       <c r="D53" s="155" t="inlineStr">
@@ -35289,7 +35314,7 @@
         </is>
       </c>
       <c r="C3" s="173">
-        <f>SUMIFS('Transactions Raw'!$F$3:$F1366,'Transactions Raw'!$E$3:$E1366,Sheet2!$B3,'Transactions Raw'!$C$3:$C1366,"&gt;="&amp;'FY26 Trail Balance'!$I$2,'Transactions Raw'!$C$3:$C1366,"&lt;="&amp;'FY26 Trail Balance'!$J$2)</f>
+        <f>SUMIFS('Transactions Raw'!$F$3:$F1367,'Transactions Raw'!$E$3:$E1367,Sheet2!$B3,'Transactions Raw'!$C$3:$C1367,"&gt;="&amp;'FY26 Trail Balance'!$I$2,'Transactions Raw'!$C$3:$C1367,"&lt;="&amp;'FY26 Trail Balance'!$J$2)</f>
         <v/>
       </c>
       <c r="D3" s="172" t="inlineStr">
